--- a/enrollment/007_education_class_registration_form--enrollment.xlsx
+++ b/enrollment/007_education_class_registration_form--enrollment.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>class_registration_form</t>
+          <t>personal_details</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Registration Form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your name?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please enter your full name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,12 +552,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Contact Information</t>
+          <t>Do you have a parent/guardian's contact number?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Enter contact information</t>
+          <t>Enter a valid phone number</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -570,19 +574,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>personal_details</t>
+          <t>class_enrollment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Personal Details</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Enter personal details</t>
-        </is>
-      </c>
+          <t>Are you a returning student?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -592,103 +592,103 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>class_enrollment</t>
+          <t>class_enrollment_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Class Enrollment</t>
+          <t>Which class do you want to enroll in?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Select which class to enroll</t>
+          <t>Select one class</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>contact_information</t>
+          <t>contact_method</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Contact Information</t>
+          <t>How would you like to be contacted?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Enter contact information</t>
+          <t>Choose one contact method</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>personal_details</t>
+          <t>date_of_birth</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Personal Details</t>
+          <t>What is your date of birth?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Enter personal details</t>
+          <t>MM/DD/YY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>class_enrollment</t>
+          <t>allergies_health_issues</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Class Enrollment</t>
+          <t>Do you have any allergies or health issues we should be aware of?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Select which class to enroll</t>
+          <t>List any allergies or health issues</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>contact_information</t>
+          <t>previous_experience</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Contact Information</t>
+          <t>Do you have any previous education experience?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -728,15 +728,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>personal_details</t>
+          <t>special_needs</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Personal Details</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Do you have any special needs requirements?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>List any special needs</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -746,27 +750,77 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>class_enrollment</t>
+          <t>contact_time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Class Enrollment</t>
+          <t>What time would you like to be contacted during the day?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Select which class to enroll</t>
+          <t>HH -MM 24-hour format</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>additional_comments</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Do you have any other comments or concerns?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please share any additional comments</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>confirmation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Do you confirm your enrollment?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -784,9 +838,9 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,102 +863,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>class_enrollment_choices</t>
+          <t>class_enrollment_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>class_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Class A</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>class_enrollment_choices</t>
+          <t>class_enrollment_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>class_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Class B</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>class_enrollment_choices</t>
+          <t>class_enrollment_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>class_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Class C</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>class_enrollment_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>class_enrollment_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>class_enrollment_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Text</t>
         </is>
       </c>
     </row>
